--- a/DesignSearch/GA-UTS-XGB/Experience.xlsx
+++ b/DesignSearch/GA-UTS-XGB/Experience.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MLDesignAl\TheFinal\DesignSearch\GA-UTS-XGB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC93F9B7-AEDD-4828-BAED-942DE85AA8E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E7DB490-37F8-4E07-989A-0EAA1358BB85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1320" yWindow="1740" windowWidth="20880" windowHeight="11388" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1152" yWindow="1128" windowWidth="20796" windowHeight="10236" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="验证实验" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="26">
   <si>
     <t>Si</t>
   </si>
@@ -93,23 +94,100 @@
     <t>UTS_pred</t>
   </si>
   <si>
-    <t>考虑Cu、Ni的密度最小</t>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>编号</t>
+    </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>无限制条件</t>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>验证模型的准确性
+但考虑到实际实验的成本与安全问题
+约束了部分元素</t>
+    </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>剔除Li</t>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">重复样：量化实验误差
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>号、7号和</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>号重复</t>
+    </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>考虑V、Zr、Ni、Sc、Ag的成本最低</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>考虑7xxx</t>
+    <r>
+      <t>Zr</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>贡献了多少强度增益？
+微合金化是在提升强度还是工艺稳定性？</t>
+    </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -120,7 +198,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0.0"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -134,6 +212,26 @@
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="3"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="2">
@@ -156,7 +254,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -172,17 +270,35 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -464,18 +580,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W6"/>
+  <dimension ref="A1:V10"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="17" width="5.44140625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="6.5546875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="9.6640625" style="6" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.33203125" style="6" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="13.44140625" style="4" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="17" width="6" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="7" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="9.77734375" style="6" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.44140625" style="6" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="13.5546875" style="4" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="10.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:22" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -543,332 +659,320 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:23" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:22" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
-        <v>5.0798000000000003E-2</v>
+        <v>0</v>
       </c>
       <c r="B2" s="2">
-        <v>5.7972000000000003E-2</v>
+        <v>0</v>
       </c>
       <c r="C2" s="2">
-        <v>2.4387089999999998</v>
+        <v>2.497541</v>
       </c>
       <c r="D2" s="2">
-        <v>1.5879000000000001E-2</v>
+        <v>4.1310000000000001E-3</v>
       </c>
       <c r="E2" s="2">
-        <v>2.5951849999999999</v>
+        <v>2.5963820000000002</v>
       </c>
       <c r="F2" s="2">
-        <v>0.19107499999999999</v>
+        <v>0</v>
       </c>
       <c r="G2" s="2">
-        <v>7.2539699999999998</v>
+        <v>7.3892499999999997</v>
       </c>
       <c r="H2" s="2">
-        <v>0.110599</v>
+        <v>0</v>
       </c>
       <c r="I2" s="2">
-        <v>1.6469999999999999E-2</v>
+        <v>5.6372999999999999E-2</v>
       </c>
       <c r="J2" s="2">
-        <v>0.166271</v>
+        <v>0.16356000000000001</v>
       </c>
       <c r="K2" s="2">
-        <v>1.2130339999999999</v>
+        <v>0</v>
       </c>
       <c r="L2" s="2">
-        <v>0.405001</v>
+        <v>0</v>
       </c>
       <c r="M2" s="2">
-        <v>1.6620000000000001E-3</v>
+        <v>3.1100000000000002E-4</v>
       </c>
       <c r="N2" s="2">
-        <v>0.18596799999999999</v>
+        <v>0.237843</v>
       </c>
       <c r="O2" s="2">
-        <v>0.332121</v>
+        <v>0</v>
       </c>
       <c r="P2" s="2">
-        <v>0.308979</v>
+        <v>0</v>
       </c>
       <c r="Q2" s="2">
-        <v>6.1683000000000002E-2</v>
+        <v>0</v>
       </c>
       <c r="R2" s="2">
-        <v>84.594622999999999</v>
+        <v>87.054609999999997</v>
       </c>
       <c r="S2" s="5">
-        <v>461.39075200000002</v>
+        <v>461.61370699999998</v>
       </c>
       <c r="T2" s="5">
-        <v>124.131856</v>
+        <v>122.741788</v>
       </c>
       <c r="U2" s="3">
-        <v>24.195929</v>
+        <v>24.003623000000001</v>
       </c>
       <c r="V2" s="2">
-        <v>717.17425500000002</v>
-      </c>
-      <c r="W2" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="3" spans="1:23" s="7" customFormat="1" x14ac:dyDescent="0.25">
+        <v>705.07252900000003</v>
+      </c>
+    </row>
+    <row r="3" spans="1:22" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
-        <v>1.0895999999999999E-2</v>
+        <v>0</v>
       </c>
       <c r="B3" s="2">
-        <v>4.5769999999999998E-2</v>
+        <v>0</v>
       </c>
       <c r="C3" s="2">
-        <v>2.433303</v>
+        <v>3.4815309999999999</v>
       </c>
       <c r="D3" s="2">
-        <v>1.6712000000000001E-2</v>
+        <v>3.0790000000000001E-3</v>
       </c>
       <c r="E3" s="2">
-        <v>2.5967220000000002</v>
+        <v>2.5963820000000002</v>
       </c>
       <c r="F3" s="2">
-        <v>0.193049</v>
+        <v>0</v>
       </c>
       <c r="G3" s="2">
-        <v>7.2717330000000002</v>
+        <v>8.4273410000000002</v>
       </c>
       <c r="H3" s="2">
-        <v>0.150507</v>
+        <v>0</v>
       </c>
       <c r="I3" s="2">
-        <v>1.0946000000000001E-2</v>
+        <v>5.4297999999999999E-2</v>
       </c>
       <c r="J3" s="2">
-        <v>0.166912</v>
+        <v>0.16545599999999999</v>
       </c>
       <c r="K3" s="2">
         <v>0</v>
       </c>
       <c r="L3" s="2">
-        <v>0.39080799999999999</v>
+        <v>0</v>
       </c>
       <c r="M3" s="2">
-        <v>7.5000000000000002E-4</v>
+        <v>5.8699999999999996E-4</v>
       </c>
       <c r="N3" s="2">
-        <v>0.228467</v>
+        <v>0.236791</v>
       </c>
       <c r="O3" s="2">
-        <v>0.53942400000000001</v>
+        <v>0</v>
       </c>
       <c r="P3" s="2">
-        <v>0.194214</v>
+        <v>0</v>
       </c>
       <c r="Q3" s="2">
-        <v>0.24764800000000001</v>
+        <v>0</v>
       </c>
       <c r="R3" s="2">
-        <v>85.502139</v>
+        <v>85.034535000000005</v>
       </c>
       <c r="S3" s="5">
-        <v>468.092422</v>
+        <v>461.61224499999997</v>
       </c>
       <c r="T3" s="5">
-        <v>106.97450000000001</v>
+        <v>122.727131</v>
       </c>
       <c r="U3" s="3">
-        <v>28.685881999999999</v>
+        <v>24.003747000000001</v>
       </c>
       <c r="V3" s="2">
-        <v>714.44107899999995</v>
-      </c>
-      <c r="W3" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="4" spans="1:23" s="7" customFormat="1" x14ac:dyDescent="0.25">
+        <v>699.91853700000001</v>
+      </c>
+    </row>
+    <row r="4" spans="1:22" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
-        <v>4.3504000000000001E-2</v>
+        <v>0</v>
       </c>
       <c r="B4" s="2">
-        <v>4.9739999999999999E-2</v>
+        <v>0</v>
       </c>
       <c r="C4" s="2">
-        <v>1.3176209999999999</v>
+        <v>2.4885190000000001</v>
       </c>
       <c r="D4" s="2">
-        <v>1.3497E-2</v>
+        <v>3.7829999999999999E-3</v>
       </c>
       <c r="E4" s="2">
-        <v>2.7692040000000002</v>
+        <v>2.596381</v>
       </c>
       <c r="F4" s="2">
-        <v>0.189835</v>
+        <v>0</v>
       </c>
       <c r="G4" s="2">
-        <v>7.5852709999999997</v>
+        <v>7.2733109999999996</v>
       </c>
       <c r="H4" s="2">
-        <v>0.158</v>
+        <v>0</v>
       </c>
       <c r="I4" s="2">
-        <v>7.5249999999999996E-3</v>
+        <v>0</v>
       </c>
       <c r="J4" s="2">
-        <v>0.17163300000000001</v>
+        <v>0.168074</v>
       </c>
       <c r="K4" s="2">
         <v>0</v>
       </c>
       <c r="L4" s="2">
-        <v>0.157196</v>
+        <v>0</v>
       </c>
       <c r="M4" s="2">
-        <v>7.1699999999999997E-4</v>
+        <v>5.8399999999999999E-4</v>
       </c>
       <c r="N4" s="2">
-        <v>0.184612</v>
+        <v>0.23813599999999999</v>
       </c>
       <c r="O4" s="2">
-        <v>0.44248599999999999</v>
+        <v>0</v>
       </c>
       <c r="P4" s="2">
-        <v>0.44845000000000002</v>
+        <v>0</v>
       </c>
       <c r="Q4" s="2">
-        <v>0.27238800000000002</v>
+        <v>0</v>
       </c>
       <c r="R4" s="2">
-        <v>86.188321999999999</v>
+        <v>87.231211999999999</v>
       </c>
       <c r="S4" s="5">
-        <v>461.25284599999998</v>
+        <v>460.851721</v>
       </c>
       <c r="T4" s="5">
-        <v>124.061763</v>
+        <v>122.722194</v>
       </c>
       <c r="U4" s="3">
-        <v>24.443307999999998</v>
+        <v>19.861281000000002</v>
       </c>
       <c r="V4" s="2">
-        <v>702.45542</v>
-      </c>
-      <c r="W4" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A5" s="8">
-        <v>1.1194000000000001E-2</v>
-      </c>
-      <c r="B5" s="8">
-        <v>4.3658000000000002E-2</v>
-      </c>
-      <c r="C5" s="8">
-        <v>2.4878209999999998</v>
-      </c>
-      <c r="D5" s="8">
-        <v>1.4054000000000001E-2</v>
-      </c>
-      <c r="E5" s="8">
-        <v>2.5949399999999998</v>
-      </c>
-      <c r="F5" s="8">
-        <v>0.19126000000000001</v>
-      </c>
-      <c r="G5" s="8">
-        <v>7.3337620000000001</v>
-      </c>
-      <c r="H5" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="I5" s="8">
-        <v>1.7295000000000001E-2</v>
-      </c>
-      <c r="J5" s="8">
-        <v>8.5537000000000002E-2</v>
-      </c>
-      <c r="K5" s="8">
-        <v>0</v>
-      </c>
-      <c r="L5" s="8">
-        <v>0.154499</v>
-      </c>
-      <c r="M5" s="8">
-        <v>1.7849999999999999E-3</v>
-      </c>
-      <c r="N5" s="8">
-        <v>0</v>
-      </c>
-      <c r="O5" s="8">
-        <v>0</v>
-      </c>
-      <c r="P5" s="8">
-        <v>0.1497</v>
-      </c>
-      <c r="Q5" s="8">
-        <v>0.110538</v>
-      </c>
-      <c r="R5" s="8">
-        <v>86.703958</v>
-      </c>
-      <c r="S5" s="10">
-        <v>468.94547499999999</v>
-      </c>
-      <c r="T5" s="10">
-        <v>106.184774</v>
-      </c>
-      <c r="U5" s="9">
-        <v>24.009005999999999</v>
-      </c>
-      <c r="V5" s="8">
-        <v>699.364643</v>
-      </c>
-      <c r="W5" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.25">
+        <v>693.71326299999998</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="2">
+        <v>0</v>
+      </c>
+      <c r="B5" s="2">
+        <v>0</v>
+      </c>
+      <c r="C5" s="2">
+        <v>2.7200229999999999</v>
+      </c>
+      <c r="D5" s="2">
+        <v>3.4489999999999998E-3</v>
+      </c>
+      <c r="E5" s="2">
+        <v>2.649848</v>
+      </c>
+      <c r="F5" s="2">
+        <v>0</v>
+      </c>
+      <c r="G5" s="2">
+        <v>7.7828799999999996</v>
+      </c>
+      <c r="H5" s="2">
+        <v>0</v>
+      </c>
+      <c r="I5" s="2">
+        <v>0.35785899999999998</v>
+      </c>
+      <c r="J5" s="2">
+        <v>0.16583700000000001</v>
+      </c>
+      <c r="K5" s="2">
+        <v>0</v>
+      </c>
+      <c r="L5" s="2">
+        <v>0</v>
+      </c>
+      <c r="M5" s="2">
+        <v>5.2499999999999997E-4</v>
+      </c>
+      <c r="N5" s="2">
+        <v>0.23849500000000001</v>
+      </c>
+      <c r="O5" s="2">
+        <v>0</v>
+      </c>
+      <c r="P5" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="2">
+        <v>0</v>
+      </c>
+      <c r="R5" s="2">
+        <v>86.081084000000004</v>
+      </c>
+      <c r="S5" s="5">
+        <v>458.80949199999998</v>
+      </c>
+      <c r="T5" s="5">
+        <v>123.131472</v>
+      </c>
+      <c r="U5" s="3">
+        <v>26.44426</v>
+      </c>
+      <c r="V5" s="2">
+        <v>687.800251</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
-        <v>5.3385000000000002E-2</v>
+        <v>0</v>
       </c>
       <c r="B6" s="2">
-        <v>5.3176000000000001E-2</v>
+        <v>0</v>
       </c>
       <c r="C6" s="2">
-        <v>2.4658479999999998</v>
+        <v>2.443746</v>
       </c>
       <c r="D6" s="2">
-        <v>1.2232E-2</v>
+        <v>2.1320000000000002E-3</v>
       </c>
       <c r="E6" s="2">
-        <v>2.5866440000000002</v>
+        <v>2.7973520000000001</v>
       </c>
       <c r="F6" s="2">
-        <v>0.19237799999999999</v>
+        <v>0</v>
       </c>
       <c r="G6" s="2">
-        <v>7.2831219999999997</v>
+        <v>7.2652390000000002</v>
       </c>
       <c r="H6" s="2">
-        <v>3.9829999999999997E-2</v>
+        <v>0</v>
       </c>
       <c r="I6" s="2">
-        <v>1.6416E-2</v>
+        <v>5.4205000000000003E-2</v>
       </c>
       <c r="J6" s="2">
-        <v>0.16436100000000001</v>
+        <v>0.12809200000000001</v>
       </c>
       <c r="K6" s="2">
         <v>0</v>
       </c>
       <c r="L6" s="2">
-        <v>7.9926999999999998E-2</v>
+        <v>0</v>
       </c>
       <c r="M6" s="2">
-        <v>9.4600000000000001E-4</v>
+        <v>7.4700000000000005E-4</v>
       </c>
       <c r="N6" s="2">
-        <v>0</v>
+        <v>0.23436399999999999</v>
       </c>
       <c r="O6" s="2">
         <v>0</v>
@@ -880,22 +984,203 @@
         <v>0</v>
       </c>
       <c r="R6" s="2">
-        <v>87.051736000000005</v>
+        <v>87.074123</v>
       </c>
       <c r="S6" s="5">
-        <v>462.57906700000001</v>
+        <v>461.572721</v>
       </c>
       <c r="T6" s="5">
-        <v>123.158368</v>
+        <v>122.771738</v>
       </c>
       <c r="U6" s="3">
-        <v>24.195633999999998</v>
+        <v>21.510774999999999</v>
       </c>
       <c r="V6" s="2">
-        <v>712.52056900000002</v>
-      </c>
-      <c r="W6" s="1" t="s">
-        <v>26</v>
+        <v>680.894678</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="2"/>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
+      <c r="H7" s="2"/>
+      <c r="I7" s="2"/>
+      <c r="J7" s="2"/>
+      <c r="K7" s="2"/>
+      <c r="L7" s="2"/>
+      <c r="M7" s="2"/>
+      <c r="N7" s="2"/>
+      <c r="O7" s="2"/>
+      <c r="P7" s="2"/>
+      <c r="Q7" s="2"/>
+      <c r="R7" s="2"/>
+      <c r="S7" s="5"/>
+      <c r="T7" s="5"/>
+      <c r="U7" s="3"/>
+      <c r="V7" s="2"/>
+    </row>
+    <row r="8" spans="1:22" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="2">
+        <v>0</v>
+      </c>
+      <c r="B8" s="2">
+        <v>0</v>
+      </c>
+      <c r="C8" s="2">
+        <v>2.4861209999999998</v>
+      </c>
+      <c r="D8" s="2">
+        <v>2.4000000000000001E-5</v>
+      </c>
+      <c r="E8" s="2">
+        <v>2.5922809999999998</v>
+      </c>
+      <c r="F8" s="2">
+        <v>1.565E-3</v>
+      </c>
+      <c r="G8" s="2">
+        <v>7.3272019999999998</v>
+      </c>
+      <c r="H8" s="2">
+        <v>1.5759999999999999E-3</v>
+      </c>
+      <c r="I8" s="2">
+        <v>5.5379999999999999E-2</v>
+      </c>
+      <c r="J8" s="2">
+        <v>0.16258800000000001</v>
+      </c>
+      <c r="K8" s="2">
+        <v>0.93932800000000005</v>
+      </c>
+      <c r="L8" s="2">
+        <v>0</v>
+      </c>
+      <c r="M8" s="2">
+        <v>7.5699999999999997E-4</v>
+      </c>
+      <c r="N8" s="2">
+        <v>0.226991</v>
+      </c>
+      <c r="O8" s="2">
+        <v>0.44630500000000001</v>
+      </c>
+      <c r="P8" s="2">
+        <v>0.241783</v>
+      </c>
+      <c r="Q8" s="2">
+        <v>2.6099999999999999E-3</v>
+      </c>
+      <c r="R8" s="2">
+        <v>85.515489000000002</v>
+      </c>
+      <c r="S8" s="5">
+        <v>463.02178700000002</v>
+      </c>
+      <c r="T8" s="5">
+        <v>124.840362</v>
+      </c>
+      <c r="U8" s="3">
+        <v>24.155540999999999</v>
+      </c>
+      <c r="V8" s="2">
+        <v>705.815068</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A9" s="2"/>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2"/>
+      <c r="J9" s="2"/>
+      <c r="K9" s="2"/>
+      <c r="L9" s="2"/>
+      <c r="M9" s="2"/>
+      <c r="N9" s="2"/>
+      <c r="O9" s="2"/>
+      <c r="P9" s="2"/>
+      <c r="Q9" s="2"/>
+      <c r="R9" s="2"/>
+      <c r="S9" s="5"/>
+      <c r="T9" s="5"/>
+      <c r="U9" s="3"/>
+      <c r="V9" s="2"/>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A10" s="2">
+        <v>0.01</v>
+      </c>
+      <c r="B10" s="2">
+        <v>0.05</v>
+      </c>
+      <c r="C10" s="2">
+        <v>2.4300000000000002</v>
+      </c>
+      <c r="D10" s="2">
+        <v>0.02</v>
+      </c>
+      <c r="E10" s="2">
+        <v>2.6</v>
+      </c>
+      <c r="F10" s="2">
+        <v>0.19</v>
+      </c>
+      <c r="G10" s="2">
+        <v>7.27</v>
+      </c>
+      <c r="H10" s="2">
+        <v>0.15</v>
+      </c>
+      <c r="I10" s="2">
+        <v>0.01</v>
+      </c>
+      <c r="J10" s="2">
+        <v>0.17</v>
+      </c>
+      <c r="K10" s="2">
+        <v>0</v>
+      </c>
+      <c r="L10" s="2">
+        <v>0.39</v>
+      </c>
+      <c r="M10" s="2">
+        <v>0</v>
+      </c>
+      <c r="N10" s="2">
+        <v>0.23</v>
+      </c>
+      <c r="O10" s="2">
+        <v>0.54</v>
+      </c>
+      <c r="P10" s="2">
+        <v>0.19</v>
+      </c>
+      <c r="Q10" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="R10" s="2">
+        <v>85.5</v>
+      </c>
+      <c r="S10" s="5">
+        <v>468</v>
+      </c>
+      <c r="T10" s="5">
+        <v>107</v>
+      </c>
+      <c r="U10" s="3">
+        <v>28.7</v>
+      </c>
+      <c r="V10" s="2">
+        <v>714.44</v>
       </c>
     </row>
   </sheetData>
@@ -903,4 +1188,653 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C107522-3658-4374-ADB5-6BA5ABF96BD6}">
+  <dimension ref="A1:V15"/>
+  <sheetFormatPr defaultRowHeight="22.8" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="8.77734375" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="7" width="8" style="10" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.88671875" style="10" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.5546875" style="10" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="20.6640625" style="10" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="19.88671875" style="10" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.33203125" style="10" bestFit="1" customWidth="1"/>
+    <col min="13" max="17" width="8.21875" style="10" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9.88671875" style="10" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="15.109375" style="10" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="21.5546875" style="10" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="20.77734375" style="10" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="16.77734375" style="10" bestFit="1" customWidth="1"/>
+    <col min="24" max="16384" width="8.88671875" style="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A1" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1" s="7" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A2" s="10">
+        <v>1</v>
+      </c>
+      <c r="B2" s="7">
+        <v>7.3892499999999997</v>
+      </c>
+      <c r="C2" s="7">
+        <v>2.5963820000000002</v>
+      </c>
+      <c r="D2" s="7">
+        <v>2.497541</v>
+      </c>
+      <c r="E2" s="7">
+        <v>0.237843</v>
+      </c>
+      <c r="F2" s="7">
+        <v>5.6372999999999999E-2</v>
+      </c>
+      <c r="G2" s="7">
+        <v>0.16356000000000001</v>
+      </c>
+      <c r="H2" s="7">
+        <v>87.054609999999997</v>
+      </c>
+      <c r="I2" s="8">
+        <v>461.61370699999998</v>
+      </c>
+      <c r="J2" s="8">
+        <v>122.741788</v>
+      </c>
+      <c r="K2" s="9">
+        <v>24.003623000000001</v>
+      </c>
+      <c r="L2" s="7">
+        <v>705.07252900000003</v>
+      </c>
+      <c r="M2" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="N2" s="15"/>
+      <c r="O2" s="15"/>
+      <c r="P2" s="15"/>
+      <c r="Q2" s="15"/>
+      <c r="R2" s="15"/>
+      <c r="S2" s="15"/>
+      <c r="T2" s="12"/>
+      <c r="U2" s="12"/>
+      <c r="V2" s="12"/>
+    </row>
+    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A3" s="10">
+        <v>2</v>
+      </c>
+      <c r="B3" s="7">
+        <v>8.4273410000000002</v>
+      </c>
+      <c r="C3" s="7">
+        <v>2.5963820000000002</v>
+      </c>
+      <c r="D3" s="7">
+        <v>3.4815309999999999</v>
+      </c>
+      <c r="E3" s="7">
+        <v>0.236791</v>
+      </c>
+      <c r="F3" s="7">
+        <v>5.4297999999999999E-2</v>
+      </c>
+      <c r="G3" s="7">
+        <v>0.16545599999999999</v>
+      </c>
+      <c r="H3" s="7">
+        <v>85.034535000000005</v>
+      </c>
+      <c r="I3" s="8">
+        <v>461.61224499999997</v>
+      </c>
+      <c r="J3" s="8">
+        <v>122.727131</v>
+      </c>
+      <c r="K3" s="9">
+        <v>24.003747000000001</v>
+      </c>
+      <c r="L3" s="7">
+        <v>699.91853700000001</v>
+      </c>
+      <c r="M3" s="15"/>
+      <c r="N3" s="15"/>
+      <c r="O3" s="15"/>
+      <c r="P3" s="15"/>
+      <c r="Q3" s="15"/>
+      <c r="R3" s="15"/>
+      <c r="S3" s="15"/>
+      <c r="T3" s="12"/>
+      <c r="U3" s="12"/>
+      <c r="V3" s="12"/>
+    </row>
+    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A4" s="10">
+        <v>3</v>
+      </c>
+      <c r="B4" s="7">
+        <v>7.2733109999999996</v>
+      </c>
+      <c r="C4" s="7">
+        <v>2.596381</v>
+      </c>
+      <c r="D4" s="7">
+        <v>2.4885190000000001</v>
+      </c>
+      <c r="E4" s="7">
+        <v>0.23813599999999999</v>
+      </c>
+      <c r="F4" s="7">
+        <v>0</v>
+      </c>
+      <c r="G4" s="7">
+        <v>0.168074</v>
+      </c>
+      <c r="H4" s="7">
+        <v>87.231211999999999</v>
+      </c>
+      <c r="I4" s="8">
+        <v>460.851721</v>
+      </c>
+      <c r="J4" s="8">
+        <v>122.722194</v>
+      </c>
+      <c r="K4" s="9">
+        <v>19.861281000000002</v>
+      </c>
+      <c r="L4" s="7">
+        <v>693.71326299999998</v>
+      </c>
+      <c r="M4" s="15"/>
+      <c r="N4" s="15"/>
+      <c r="O4" s="15"/>
+      <c r="P4" s="15"/>
+      <c r="Q4" s="15"/>
+      <c r="R4" s="15"/>
+      <c r="S4" s="15"/>
+      <c r="T4" s="12"/>
+      <c r="U4" s="12"/>
+      <c r="V4" s="12"/>
+    </row>
+    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A5" s="10">
+        <v>4</v>
+      </c>
+      <c r="B5" s="7">
+        <v>7.7828799999999996</v>
+      </c>
+      <c r="C5" s="7">
+        <v>2.649848</v>
+      </c>
+      <c r="D5" s="7">
+        <v>2.7200229999999999</v>
+      </c>
+      <c r="E5" s="7">
+        <v>0.23849500000000001</v>
+      </c>
+      <c r="F5" s="7">
+        <v>0.35785899999999998</v>
+      </c>
+      <c r="G5" s="7">
+        <v>0.16583700000000001</v>
+      </c>
+      <c r="H5" s="7">
+        <v>86.081084000000004</v>
+      </c>
+      <c r="I5" s="8">
+        <v>458.80949199999998</v>
+      </c>
+      <c r="J5" s="8">
+        <v>123.131472</v>
+      </c>
+      <c r="K5" s="9">
+        <v>26.44426</v>
+      </c>
+      <c r="L5" s="7">
+        <v>687.800251</v>
+      </c>
+      <c r="M5" s="15"/>
+      <c r="N5" s="15"/>
+      <c r="O5" s="15"/>
+      <c r="P5" s="15"/>
+      <c r="Q5" s="15"/>
+      <c r="R5" s="15"/>
+      <c r="S5" s="15"/>
+      <c r="T5" s="12"/>
+      <c r="U5" s="12"/>
+      <c r="V5" s="12"/>
+    </row>
+    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A6" s="10">
+        <v>5</v>
+      </c>
+      <c r="B6" s="7">
+        <v>7.2652390000000002</v>
+      </c>
+      <c r="C6" s="7">
+        <v>2.7973520000000001</v>
+      </c>
+      <c r="D6" s="7">
+        <v>2.443746</v>
+      </c>
+      <c r="E6" s="7">
+        <v>0.23436399999999999</v>
+      </c>
+      <c r="F6" s="7">
+        <v>5.4205000000000003E-2</v>
+      </c>
+      <c r="G6" s="7">
+        <v>0.12809200000000001</v>
+      </c>
+      <c r="H6" s="7">
+        <v>87.074123</v>
+      </c>
+      <c r="I6" s="8">
+        <v>461.572721</v>
+      </c>
+      <c r="J6" s="8">
+        <v>122.771738</v>
+      </c>
+      <c r="K6" s="9">
+        <v>21.510774999999999</v>
+      </c>
+      <c r="L6" s="7">
+        <v>680.894678</v>
+      </c>
+      <c r="M6" s="15"/>
+      <c r="N6" s="15"/>
+      <c r="O6" s="15"/>
+      <c r="P6" s="15"/>
+      <c r="Q6" s="15"/>
+      <c r="R6" s="15"/>
+      <c r="S6" s="15"/>
+      <c r="T6" s="12"/>
+      <c r="U6" s="12"/>
+      <c r="V6" s="12"/>
+    </row>
+    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="B7" s="7"/>
+      <c r="C7" s="7"/>
+      <c r="D7" s="7"/>
+      <c r="E7" s="7"/>
+      <c r="F7" s="7"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="7"/>
+      <c r="I7" s="8"/>
+      <c r="J7" s="8"/>
+      <c r="K7" s="9"/>
+      <c r="L7" s="7"/>
+      <c r="M7" s="11"/>
+      <c r="N7" s="11"/>
+      <c r="O7" s="11"/>
+      <c r="P7" s="11"/>
+      <c r="Q7" s="11"/>
+      <c r="R7" s="11"/>
+      <c r="S7" s="11"/>
+      <c r="T7" s="11"/>
+      <c r="U7" s="11"/>
+      <c r="V7" s="11"/>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A8" s="10">
+        <v>6</v>
+      </c>
+      <c r="B8" s="7">
+        <v>7.2733109999999996</v>
+      </c>
+      <c r="C8" s="7">
+        <v>2.596381</v>
+      </c>
+      <c r="D8" s="7">
+        <v>2.4885190000000001</v>
+      </c>
+      <c r="E8" s="7">
+        <v>0.23813599999999999</v>
+      </c>
+      <c r="F8" s="7">
+        <v>0</v>
+      </c>
+      <c r="G8" s="7">
+        <v>0.168074</v>
+      </c>
+      <c r="H8" s="7">
+        <v>87.231211999999999</v>
+      </c>
+      <c r="I8" s="8">
+        <v>460.851721</v>
+      </c>
+      <c r="J8" s="8">
+        <v>122.722194</v>
+      </c>
+      <c r="K8" s="9">
+        <v>19.861281000000002</v>
+      </c>
+      <c r="L8" s="7">
+        <v>693.71326299999998</v>
+      </c>
+      <c r="M8" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="N8" s="16"/>
+      <c r="O8" s="16"/>
+      <c r="P8" s="16"/>
+      <c r="Q8" s="16"/>
+      <c r="R8" s="16"/>
+      <c r="S8" s="16"/>
+      <c r="T8" s="14"/>
+      <c r="U8" s="14"/>
+      <c r="V8" s="14"/>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A9" s="10">
+        <v>7</v>
+      </c>
+      <c r="B9" s="7">
+        <v>7.2733109999999996</v>
+      </c>
+      <c r="C9" s="7">
+        <v>2.596381</v>
+      </c>
+      <c r="D9" s="7">
+        <v>2.4885190000000001</v>
+      </c>
+      <c r="E9" s="7">
+        <v>0.23813599999999999</v>
+      </c>
+      <c r="F9" s="7">
+        <v>0</v>
+      </c>
+      <c r="G9" s="7">
+        <v>0.168074</v>
+      </c>
+      <c r="H9" s="7">
+        <v>87.231211999999999</v>
+      </c>
+      <c r="I9" s="8">
+        <v>460.851721</v>
+      </c>
+      <c r="J9" s="8">
+        <v>122.722194</v>
+      </c>
+      <c r="K9" s="9">
+        <v>19.861281000000002</v>
+      </c>
+      <c r="L9" s="7">
+        <v>693.71326299999998</v>
+      </c>
+      <c r="M9" s="16"/>
+      <c r="N9" s="16"/>
+      <c r="O9" s="16"/>
+      <c r="P9" s="16"/>
+      <c r="Q9" s="16"/>
+      <c r="R9" s="16"/>
+      <c r="S9" s="16"/>
+      <c r="T9" s="14"/>
+      <c r="U9" s="14"/>
+      <c r="V9" s="14"/>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="B10" s="7"/>
+      <c r="C10" s="7"/>
+      <c r="D10" s="7"/>
+      <c r="E10" s="7"/>
+      <c r="F10" s="7"/>
+      <c r="G10" s="7"/>
+      <c r="H10" s="7"/>
+      <c r="I10" s="8"/>
+      <c r="J10" s="8"/>
+      <c r="K10" s="9"/>
+      <c r="L10" s="7"/>
+      <c r="M10" s="7"/>
+      <c r="N10" s="7"/>
+      <c r="O10" s="7"/>
+      <c r="P10" s="7"/>
+      <c r="Q10" s="7"/>
+      <c r="R10" s="7"/>
+      <c r="S10" s="7"/>
+      <c r="T10" s="7"/>
+      <c r="U10" s="7"/>
+      <c r="V10" s="7"/>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A11" s="10">
+        <v>8</v>
+      </c>
+      <c r="B11" s="7">
+        <v>7.3892499999999997</v>
+      </c>
+      <c r="C11" s="7">
+        <v>2.5963820000000002</v>
+      </c>
+      <c r="D11" s="7">
+        <v>2.497541</v>
+      </c>
+      <c r="E11" s="7">
+        <v>0.237843</v>
+      </c>
+      <c r="F11" s="7">
+        <v>5.6372999999999999E-2</v>
+      </c>
+      <c r="G11" s="7">
+        <v>0</v>
+      </c>
+      <c r="H11" s="7">
+        <v>87.21</v>
+      </c>
+      <c r="I11" s="8">
+        <v>461.61370699999998</v>
+      </c>
+      <c r="J11" s="8">
+        <v>122.741788</v>
+      </c>
+      <c r="K11" s="9">
+        <v>24.003623000000001</v>
+      </c>
+      <c r="L11" s="7">
+        <v>655.86</v>
+      </c>
+      <c r="M11" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="N11" s="15"/>
+      <c r="O11" s="15"/>
+      <c r="P11" s="15"/>
+      <c r="Q11" s="15"/>
+      <c r="R11" s="15"/>
+      <c r="S11" s="15"/>
+      <c r="T11" s="13"/>
+      <c r="U11" s="13"/>
+      <c r="V11" s="13"/>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A12" s="10">
+        <v>9</v>
+      </c>
+      <c r="B12" s="7">
+        <v>7.2733109999999996</v>
+      </c>
+      <c r="C12" s="7">
+        <v>2.596381</v>
+      </c>
+      <c r="D12" s="7">
+        <v>2.4885190000000001</v>
+      </c>
+      <c r="E12" s="7">
+        <v>0.23813599999999999</v>
+      </c>
+      <c r="F12" s="7">
+        <v>0</v>
+      </c>
+      <c r="G12" s="7">
+        <v>0</v>
+      </c>
+      <c r="H12" s="7">
+        <v>87.4</v>
+      </c>
+      <c r="I12" s="8">
+        <v>460.851721</v>
+      </c>
+      <c r="J12" s="8">
+        <v>122.722194</v>
+      </c>
+      <c r="K12" s="9">
+        <v>19.861281000000002</v>
+      </c>
+      <c r="L12" s="7">
+        <v>650.63</v>
+      </c>
+      <c r="M12" s="15"/>
+      <c r="N12" s="15"/>
+      <c r="O12" s="15"/>
+      <c r="P12" s="15"/>
+      <c r="Q12" s="15"/>
+      <c r="R12" s="15"/>
+      <c r="S12" s="15"/>
+      <c r="T12" s="13"/>
+      <c r="U12" s="13"/>
+      <c r="V12" s="13"/>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A13" s="10">
+        <v>10</v>
+      </c>
+      <c r="B13" s="7">
+        <v>7.2652390000000002</v>
+      </c>
+      <c r="C13" s="7">
+        <v>2.7973520000000001</v>
+      </c>
+      <c r="D13" s="7">
+        <v>2.443746</v>
+      </c>
+      <c r="E13" s="7">
+        <v>0.23436399999999999</v>
+      </c>
+      <c r="F13" s="7">
+        <v>5.4205000000000003E-2</v>
+      </c>
+      <c r="G13" s="7">
+        <v>0</v>
+      </c>
+      <c r="H13" s="7">
+        <v>87.21</v>
+      </c>
+      <c r="I13" s="8">
+        <v>461.572721</v>
+      </c>
+      <c r="J13" s="8">
+        <v>122.771738</v>
+      </c>
+      <c r="K13" s="9">
+        <v>21.510774999999999</v>
+      </c>
+      <c r="L13" s="7">
+        <v>654.62</v>
+      </c>
+      <c r="M13" s="15"/>
+      <c r="N13" s="15"/>
+      <c r="O13" s="15"/>
+      <c r="P13" s="15"/>
+      <c r="Q13" s="15"/>
+      <c r="R13" s="15"/>
+      <c r="S13" s="15"/>
+      <c r="T13" s="13"/>
+      <c r="U13" s="13"/>
+      <c r="V13" s="13"/>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="B14" s="7"/>
+      <c r="C14" s="7"/>
+      <c r="D14" s="7"/>
+      <c r="E14" s="7"/>
+      <c r="F14" s="7"/>
+      <c r="G14" s="7"/>
+      <c r="H14" s="7"/>
+      <c r="I14" s="7"/>
+      <c r="J14" s="7"/>
+      <c r="K14" s="7"/>
+      <c r="L14" s="7"/>
+      <c r="M14" s="7"/>
+      <c r="N14" s="7"/>
+      <c r="O14" s="7"/>
+      <c r="P14" s="7"/>
+      <c r="Q14" s="7"/>
+      <c r="R14" s="7"/>
+      <c r="S14" s="7"/>
+      <c r="T14" s="7"/>
+      <c r="U14" s="7"/>
+      <c r="V14" s="7"/>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="B15" s="7"/>
+      <c r="C15" s="7"/>
+      <c r="D15" s="7"/>
+      <c r="E15" s="7"/>
+      <c r="F15" s="7"/>
+      <c r="G15" s="7"/>
+      <c r="H15" s="7"/>
+      <c r="I15" s="7"/>
+      <c r="J15" s="7"/>
+      <c r="K15" s="7"/>
+      <c r="L15" s="7"/>
+      <c r="M15" s="7"/>
+      <c r="N15" s="7"/>
+      <c r="O15" s="7"/>
+      <c r="P15" s="7"/>
+      <c r="Q15" s="7"/>
+      <c r="R15" s="7"/>
+      <c r="S15" s="8"/>
+      <c r="T15" s="8"/>
+      <c r="U15" s="9"/>
+      <c r="V15" s="7"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="M2:S6"/>
+    <mergeCell ref="M8:S9"/>
+    <mergeCell ref="M11:S13"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>
--- a/DesignSearch/GA-UTS-XGB/Experience.xlsx
+++ b/DesignSearch/GA-UTS-XGB/Experience.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MLDesignAl\TheFinal\DesignSearch\GA-UTS-XGB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E7DB490-37F8-4E07-989A-0EAA1358BB85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FA561F1-8727-4C19-9D1C-10C70AF9AD8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1152" yWindow="1128" windowWidth="20796" windowHeight="10236" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="30720" yWindow="1920" windowWidth="21600" windowHeight="11235" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="29">
   <si>
     <t>Si</t>
   </si>
@@ -190,6 +190,107 @@
     </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">验证模型的准确性
+但考虑到实际实验的成本与安全问题
+约束了部分元素
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>1-5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>号为</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Al-Cu</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>系，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>号为</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Al-Zn-Mg-Cu</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>系</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>超出训练集最大值进行预测</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>重复样：量化实验误差
+8、9、10号重复</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -234,12 +335,18 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -254,7 +361,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -294,11 +401,26 @@
     <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1192,7 +1314,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C107522-3658-4374-ADB5-6BA5ABF96BD6}">
-  <dimension ref="A1:V15"/>
+  <dimension ref="A1:V27"/>
   <sheetFormatPr defaultRowHeight="22.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.77734375" style="10" bestFit="1" customWidth="1"/>
@@ -1286,15 +1408,15 @@
       <c r="L2" s="7">
         <v>705.07252900000003</v>
       </c>
-      <c r="M2" s="15" t="s">
+      <c r="M2" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="N2" s="15"/>
-      <c r="O2" s="15"/>
-      <c r="P2" s="15"/>
-      <c r="Q2" s="15"/>
-      <c r="R2" s="15"/>
-      <c r="S2" s="15"/>
+      <c r="N2" s="17"/>
+      <c r="O2" s="17"/>
+      <c r="P2" s="17"/>
+      <c r="Q2" s="17"/>
+      <c r="R2" s="17"/>
+      <c r="S2" s="17"/>
       <c r="T2" s="12"/>
       <c r="U2" s="12"/>
       <c r="V2" s="12"/>
@@ -1336,13 +1458,13 @@
       <c r="L3" s="7">
         <v>699.91853700000001</v>
       </c>
-      <c r="M3" s="15"/>
-      <c r="N3" s="15"/>
-      <c r="O3" s="15"/>
-      <c r="P3" s="15"/>
-      <c r="Q3" s="15"/>
-      <c r="R3" s="15"/>
-      <c r="S3" s="15"/>
+      <c r="M3" s="17"/>
+      <c r="N3" s="17"/>
+      <c r="O3" s="17"/>
+      <c r="P3" s="17"/>
+      <c r="Q3" s="17"/>
+      <c r="R3" s="17"/>
+      <c r="S3" s="17"/>
       <c r="T3" s="12"/>
       <c r="U3" s="12"/>
       <c r="V3" s="12"/>
@@ -1384,13 +1506,13 @@
       <c r="L4" s="7">
         <v>693.71326299999998</v>
       </c>
-      <c r="M4" s="15"/>
-      <c r="N4" s="15"/>
-      <c r="O4" s="15"/>
-      <c r="P4" s="15"/>
-      <c r="Q4" s="15"/>
-      <c r="R4" s="15"/>
-      <c r="S4" s="15"/>
+      <c r="M4" s="17"/>
+      <c r="N4" s="17"/>
+      <c r="O4" s="17"/>
+      <c r="P4" s="17"/>
+      <c r="Q4" s="17"/>
+      <c r="R4" s="17"/>
+      <c r="S4" s="17"/>
       <c r="T4" s="12"/>
       <c r="U4" s="12"/>
       <c r="V4" s="12"/>
@@ -1432,13 +1554,13 @@
       <c r="L5" s="7">
         <v>687.800251</v>
       </c>
-      <c r="M5" s="15"/>
-      <c r="N5" s="15"/>
-      <c r="O5" s="15"/>
-      <c r="P5" s="15"/>
-      <c r="Q5" s="15"/>
-      <c r="R5" s="15"/>
-      <c r="S5" s="15"/>
+      <c r="M5" s="17"/>
+      <c r="N5" s="17"/>
+      <c r="O5" s="17"/>
+      <c r="P5" s="17"/>
+      <c r="Q5" s="17"/>
+      <c r="R5" s="17"/>
+      <c r="S5" s="17"/>
       <c r="T5" s="12"/>
       <c r="U5" s="12"/>
       <c r="V5" s="12"/>
@@ -1480,13 +1602,13 @@
       <c r="L6" s="7">
         <v>680.894678</v>
       </c>
-      <c r="M6" s="15"/>
-      <c r="N6" s="15"/>
-      <c r="O6" s="15"/>
-      <c r="P6" s="15"/>
-      <c r="Q6" s="15"/>
-      <c r="R6" s="15"/>
-      <c r="S6" s="15"/>
+      <c r="M6" s="17"/>
+      <c r="N6" s="17"/>
+      <c r="O6" s="17"/>
+      <c r="P6" s="17"/>
+      <c r="Q6" s="17"/>
+      <c r="R6" s="17"/>
+      <c r="S6" s="17"/>
       <c r="T6" s="12"/>
       <c r="U6" s="12"/>
       <c r="V6" s="12"/>
@@ -1672,15 +1794,15 @@
       <c r="L11" s="7">
         <v>655.86</v>
       </c>
-      <c r="M11" s="15" t="s">
+      <c r="M11" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="N11" s="15"/>
-      <c r="O11" s="15"/>
-      <c r="P11" s="15"/>
-      <c r="Q11" s="15"/>
-      <c r="R11" s="15"/>
-      <c r="S11" s="15"/>
+      <c r="N11" s="17"/>
+      <c r="O11" s="17"/>
+      <c r="P11" s="17"/>
+      <c r="Q11" s="17"/>
+      <c r="R11" s="17"/>
+      <c r="S11" s="17"/>
       <c r="T11" s="13"/>
       <c r="U11" s="13"/>
       <c r="V11" s="13"/>
@@ -1722,13 +1844,13 @@
       <c r="L12" s="7">
         <v>650.63</v>
       </c>
-      <c r="M12" s="15"/>
-      <c r="N12" s="15"/>
-      <c r="O12" s="15"/>
-      <c r="P12" s="15"/>
-      <c r="Q12" s="15"/>
-      <c r="R12" s="15"/>
-      <c r="S12" s="15"/>
+      <c r="M12" s="17"/>
+      <c r="N12" s="17"/>
+      <c r="O12" s="17"/>
+      <c r="P12" s="17"/>
+      <c r="Q12" s="17"/>
+      <c r="R12" s="17"/>
+      <c r="S12" s="17"/>
       <c r="T12" s="13"/>
       <c r="U12" s="13"/>
       <c r="V12" s="13"/>
@@ -1770,13 +1892,13 @@
       <c r="L13" s="7">
         <v>654.62</v>
       </c>
-      <c r="M13" s="15"/>
-      <c r="N13" s="15"/>
-      <c r="O13" s="15"/>
-      <c r="P13" s="15"/>
-      <c r="Q13" s="15"/>
-      <c r="R13" s="15"/>
-      <c r="S13" s="15"/>
+      <c r="M13" s="17"/>
+      <c r="N13" s="17"/>
+      <c r="O13" s="17"/>
+      <c r="P13" s="17"/>
+      <c r="Q13" s="17"/>
+      <c r="R13" s="17"/>
+      <c r="S13" s="17"/>
       <c r="T13" s="13"/>
       <c r="U13" s="13"/>
       <c r="V13" s="13"/>
@@ -1805,17 +1927,42 @@
       <c r="V14" s="7"/>
     </row>
     <row r="15" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="B15" s="7"/>
-      <c r="C15" s="7"/>
-      <c r="D15" s="7"/>
-      <c r="E15" s="7"/>
-      <c r="F15" s="7"/>
-      <c r="G15" s="7"/>
-      <c r="H15" s="7"/>
-      <c r="I15" s="7"/>
-      <c r="J15" s="7"/>
-      <c r="K15" s="7"/>
-      <c r="L15" s="7"/>
+      <c r="A15" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="G15" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="H15" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="I15" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="J15" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="K15" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="L15" s="7" t="s">
+        <v>21</v>
+      </c>
       <c r="M15" s="7"/>
       <c r="N15" s="7"/>
       <c r="O15" s="7"/>
@@ -1827,11 +1974,483 @@
       <c r="U15" s="9"/>
       <c r="V15" s="7"/>
     </row>
+    <row r="16" spans="1:22" ht="22.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="18">
+        <v>1</v>
+      </c>
+      <c r="B16" s="19">
+        <v>0</v>
+      </c>
+      <c r="C16" s="19">
+        <v>0.117345</v>
+      </c>
+      <c r="D16" s="19">
+        <v>7.0828069999999999</v>
+      </c>
+      <c r="E16" s="19">
+        <v>0.13770299999999999</v>
+      </c>
+      <c r="F16" s="19">
+        <v>5.0457000000000002E-2</v>
+      </c>
+      <c r="G16" s="19">
+        <v>0</v>
+      </c>
+      <c r="H16" s="19">
+        <v>92.611688000000001</v>
+      </c>
+      <c r="I16" s="20">
+        <v>523.49421099999995</v>
+      </c>
+      <c r="J16" s="20">
+        <v>306.16425299999997</v>
+      </c>
+      <c r="K16" s="21">
+        <v>5.0267999999999997</v>
+      </c>
+      <c r="L16" s="19">
+        <v>198.88639800000001</v>
+      </c>
+      <c r="M16" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="N16" s="17"/>
+      <c r="O16" s="17"/>
+      <c r="P16" s="17"/>
+      <c r="Q16" s="17"/>
+      <c r="R16" s="17"/>
+      <c r="S16" s="17"/>
+    </row>
+    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A17" s="18">
+        <v>2</v>
+      </c>
+      <c r="B17" s="19">
+        <v>2.7545459999999999</v>
+      </c>
+      <c r="C17" s="19">
+        <v>0.869448</v>
+      </c>
+      <c r="D17" s="19">
+        <v>6.7877109999999998</v>
+      </c>
+      <c r="E17" s="19">
+        <v>6.5535999999999997E-2</v>
+      </c>
+      <c r="F17" s="19">
+        <v>4.3603999999999997E-2</v>
+      </c>
+      <c r="G17" s="19">
+        <v>9.3499999999999996E-4</v>
+      </c>
+      <c r="H17" s="19">
+        <v>89.478219999999993</v>
+      </c>
+      <c r="I17" s="20">
+        <v>520.40509699999996</v>
+      </c>
+      <c r="J17" s="20">
+        <v>275.48826500000001</v>
+      </c>
+      <c r="K17" s="21">
+        <v>9.3545940000000005</v>
+      </c>
+      <c r="L17" s="19">
+        <v>299.90802000000002</v>
+      </c>
+      <c r="M17" s="17"/>
+      <c r="N17" s="17"/>
+      <c r="O17" s="17"/>
+      <c r="P17" s="17"/>
+      <c r="Q17" s="17"/>
+      <c r="R17" s="17"/>
+      <c r="S17" s="17"/>
+    </row>
+    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A18" s="18">
+        <v>3</v>
+      </c>
+      <c r="B18" s="19">
+        <v>2.202499</v>
+      </c>
+      <c r="C18" s="19">
+        <v>1.3599399999999999</v>
+      </c>
+      <c r="D18" s="19">
+        <v>7.0022760000000002</v>
+      </c>
+      <c r="E18" s="19">
+        <v>0</v>
+      </c>
+      <c r="F18" s="19">
+        <v>5.3226999999999997E-2</v>
+      </c>
+      <c r="G18" s="19">
+        <v>0.13575000000000001</v>
+      </c>
+      <c r="H18" s="19">
+        <v>89.246307999999999</v>
+      </c>
+      <c r="I18" s="20">
+        <v>520.17504399999996</v>
+      </c>
+      <c r="J18" s="20">
+        <v>272.92353800000001</v>
+      </c>
+      <c r="K18" s="21">
+        <v>8.0743200000000002</v>
+      </c>
+      <c r="L18" s="19">
+        <v>400.101562</v>
+      </c>
+      <c r="M18" s="17"/>
+      <c r="N18" s="17"/>
+      <c r="O18" s="17"/>
+      <c r="P18" s="17"/>
+      <c r="Q18" s="17"/>
+      <c r="R18" s="17"/>
+      <c r="S18" s="17"/>
+    </row>
+    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A19" s="18">
+        <v>4</v>
+      </c>
+      <c r="B19" s="19">
+        <v>4.3163929999999997</v>
+      </c>
+      <c r="C19" s="19">
+        <v>2.0737839999999998</v>
+      </c>
+      <c r="D19" s="19">
+        <v>6.4016719999999996</v>
+      </c>
+      <c r="E19" s="19">
+        <v>3.1909999999999998E-3</v>
+      </c>
+      <c r="F19" s="19">
+        <v>3.4314999999999998E-2</v>
+      </c>
+      <c r="G19" s="19">
+        <v>9.8548999999999998E-2</v>
+      </c>
+      <c r="H19" s="19">
+        <v>87.072096000000002</v>
+      </c>
+      <c r="I19" s="20">
+        <v>421.56461400000001</v>
+      </c>
+      <c r="J19" s="20">
+        <v>172.80068900000001</v>
+      </c>
+      <c r="K19" s="21">
+        <v>10.037141999999999</v>
+      </c>
+      <c r="L19" s="19">
+        <v>500.01162699999998</v>
+      </c>
+      <c r="M19" s="17"/>
+      <c r="N19" s="17"/>
+      <c r="O19" s="17"/>
+      <c r="P19" s="17"/>
+      <c r="Q19" s="17"/>
+      <c r="R19" s="17"/>
+      <c r="S19" s="17"/>
+    </row>
+    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A20" s="18">
+        <v>5</v>
+      </c>
+      <c r="B20" s="19">
+        <v>5.5428069999999998</v>
+      </c>
+      <c r="C20" s="19">
+        <v>2.5891519999999999</v>
+      </c>
+      <c r="D20" s="19">
+        <v>6.5263540000000004</v>
+      </c>
+      <c r="E20" s="19">
+        <v>0.17667099999999999</v>
+      </c>
+      <c r="F20" s="19">
+        <v>4.8640999999999997E-2</v>
+      </c>
+      <c r="G20" s="19">
+        <v>0.115828</v>
+      </c>
+      <c r="H20" s="19">
+        <v>85.000546999999997</v>
+      </c>
+      <c r="I20" s="20">
+        <v>469.28150699999998</v>
+      </c>
+      <c r="J20" s="20">
+        <v>117.077184</v>
+      </c>
+      <c r="K20" s="21">
+        <v>9.0460560000000001</v>
+      </c>
+      <c r="L20" s="19">
+        <v>600.35815400000001</v>
+      </c>
+      <c r="M20" s="17"/>
+      <c r="N20" s="17"/>
+      <c r="O20" s="17"/>
+      <c r="P20" s="17"/>
+      <c r="Q20" s="17"/>
+      <c r="R20" s="17"/>
+      <c r="S20" s="17"/>
+    </row>
+    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A21" s="10">
+        <v>6</v>
+      </c>
+      <c r="B21" s="7">
+        <v>7.2270029999999998</v>
+      </c>
+      <c r="C21" s="7">
+        <v>2.721257</v>
+      </c>
+      <c r="D21" s="7">
+        <v>2.4815330000000002</v>
+      </c>
+      <c r="E21" s="7">
+        <v>0.23458200000000001</v>
+      </c>
+      <c r="F21" s="7">
+        <v>2.6695E-2</v>
+      </c>
+      <c r="G21" s="7">
+        <v>0.13309099999999999</v>
+      </c>
+      <c r="H21" s="7">
+        <v>87.175265999999993</v>
+      </c>
+      <c r="I21" s="8">
+        <v>459.70979899999998</v>
+      </c>
+      <c r="J21" s="8">
+        <v>174.32436899999999</v>
+      </c>
+      <c r="K21" s="9">
+        <v>24.004154</v>
+      </c>
+      <c r="L21" s="7">
+        <v>596.45180100000005</v>
+      </c>
+      <c r="M21" s="17"/>
+      <c r="N21" s="17"/>
+      <c r="O21" s="17"/>
+      <c r="P21" s="17"/>
+      <c r="Q21" s="17"/>
+      <c r="R21" s="17"/>
+      <c r="S21" s="17"/>
+    </row>
+    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A23" s="10">
+        <v>7</v>
+      </c>
+      <c r="B23" s="7">
+        <v>7.2652390000000002</v>
+      </c>
+      <c r="C23" s="7">
+        <v>2.7973520000000001</v>
+      </c>
+      <c r="D23" s="7">
+        <v>2.443746</v>
+      </c>
+      <c r="E23" s="7">
+        <v>0.23436399999999999</v>
+      </c>
+      <c r="F23" s="7">
+        <v>5.4205000000000003E-2</v>
+      </c>
+      <c r="G23" s="7">
+        <v>0.12809200000000001</v>
+      </c>
+      <c r="H23" s="7">
+        <v>87.074123</v>
+      </c>
+      <c r="I23" s="8">
+        <v>461.572721</v>
+      </c>
+      <c r="J23" s="8">
+        <v>122.771738</v>
+      </c>
+      <c r="K23" s="9">
+        <v>21.510774999999999</v>
+      </c>
+      <c r="L23" s="7">
+        <v>680.894678</v>
+      </c>
+      <c r="M23" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="N23" s="16"/>
+      <c r="O23" s="16"/>
+      <c r="P23" s="16"/>
+      <c r="Q23" s="16"/>
+      <c r="R23" s="16"/>
+      <c r="S23" s="16"/>
+    </row>
+    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A24" s="18">
+        <v>8</v>
+      </c>
+      <c r="B24" s="19">
+        <v>7.3892499999999997</v>
+      </c>
+      <c r="C24" s="19">
+        <v>2.5963820000000002</v>
+      </c>
+      <c r="D24" s="19">
+        <v>2.497541</v>
+      </c>
+      <c r="E24" s="19">
+        <v>0.237843</v>
+      </c>
+      <c r="F24" s="19">
+        <v>5.6372999999999999E-2</v>
+      </c>
+      <c r="G24" s="19">
+        <v>0.16356000000000001</v>
+      </c>
+      <c r="H24" s="19">
+        <v>87.054609999999997</v>
+      </c>
+      <c r="I24" s="20">
+        <v>461.61370699999998</v>
+      </c>
+      <c r="J24" s="20">
+        <v>122.741788</v>
+      </c>
+      <c r="K24" s="21">
+        <v>24.003623000000001</v>
+      </c>
+      <c r="L24" s="19">
+        <v>705.07252900000003</v>
+      </c>
+      <c r="M24" s="16"/>
+      <c r="N24" s="16"/>
+      <c r="O24" s="16"/>
+      <c r="P24" s="16"/>
+      <c r="Q24" s="16"/>
+      <c r="R24" s="16"/>
+      <c r="S24" s="16"/>
+    </row>
+    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="B25" s="7"/>
+      <c r="C25" s="7"/>
+      <c r="D25" s="7"/>
+      <c r="E25" s="7"/>
+      <c r="F25" s="7"/>
+      <c r="G25" s="7"/>
+      <c r="H25" s="7"/>
+      <c r="I25" s="8"/>
+      <c r="J25" s="8"/>
+      <c r="K25" s="9"/>
+      <c r="L25" s="7"/>
+    </row>
+    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A26" s="10">
+        <v>9</v>
+      </c>
+      <c r="B26" s="7">
+        <v>7.3892499999999997</v>
+      </c>
+      <c r="C26" s="7">
+        <v>2.5963820000000002</v>
+      </c>
+      <c r="D26" s="7">
+        <v>2.497541</v>
+      </c>
+      <c r="E26" s="7">
+        <v>0.237843</v>
+      </c>
+      <c r="F26" s="7">
+        <v>5.6372999999999999E-2</v>
+      </c>
+      <c r="G26" s="7">
+        <v>0.16356000000000001</v>
+      </c>
+      <c r="H26" s="7">
+        <v>87.054609999999997</v>
+      </c>
+      <c r="I26" s="8">
+        <v>461.61370699999998</v>
+      </c>
+      <c r="J26" s="8">
+        <v>122.741788</v>
+      </c>
+      <c r="K26" s="9">
+        <v>24.003623000000001</v>
+      </c>
+      <c r="L26" s="7">
+        <v>705.07252900000003</v>
+      </c>
+      <c r="M26" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="N26" s="16"/>
+      <c r="O26" s="16"/>
+      <c r="P26" s="16"/>
+      <c r="Q26" s="16"/>
+      <c r="R26" s="16"/>
+      <c r="S26" s="16"/>
+    </row>
+    <row r="27" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A27" s="10">
+        <v>10</v>
+      </c>
+      <c r="B27" s="7">
+        <v>7.3892499999999997</v>
+      </c>
+      <c r="C27" s="7">
+        <v>2.5963820000000002</v>
+      </c>
+      <c r="D27" s="7">
+        <v>2.497541</v>
+      </c>
+      <c r="E27" s="7">
+        <v>0.237843</v>
+      </c>
+      <c r="F27" s="7">
+        <v>5.6372999999999999E-2</v>
+      </c>
+      <c r="G27" s="7">
+        <v>0.16356000000000001</v>
+      </c>
+      <c r="H27" s="7">
+        <v>87.054609999999997</v>
+      </c>
+      <c r="I27" s="8">
+        <v>461.61370699999998</v>
+      </c>
+      <c r="J27" s="8">
+        <v>122.741788</v>
+      </c>
+      <c r="K27" s="9">
+        <v>24.003623000000001</v>
+      </c>
+      <c r="L27" s="7">
+        <v>705.07252900000003</v>
+      </c>
+      <c r="M27" s="16"/>
+      <c r="N27" s="16"/>
+      <c r="O27" s="16"/>
+      <c r="P27" s="16"/>
+      <c r="Q27" s="16"/>
+      <c r="R27" s="16"/>
+      <c r="S27" s="16"/>
+    </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="6">
+    <mergeCell ref="M23:S24"/>
+    <mergeCell ref="M26:S27"/>
     <mergeCell ref="M2:S6"/>
     <mergeCell ref="M8:S9"/>
     <mergeCell ref="M11:S13"/>
+    <mergeCell ref="M16:S21"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/DesignSearch/GA-UTS-XGB/Experience.xlsx
+++ b/DesignSearch/GA-UTS-XGB/Experience.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MLDesignAl\TheFinal\DesignSearch\GA-UTS-XGB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FA561F1-8727-4C19-9D1C-10C70AF9AD8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87C3554F-4E56-4D61-9E51-5E0F6ACA66E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30720" yWindow="1920" windowWidth="21600" windowHeight="11235" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="31755" yWindow="2355" windowWidth="19335" windowHeight="11595" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="50">
   <si>
     <t>Si</t>
   </si>
@@ -291,6 +291,109 @@
 8、9、10号重复</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>460℃×5h+500℃×18h</t>
+  </si>
+  <si>
+    <t>520℃×2h</t>
+  </si>
+  <si>
+    <t>306℃×5h</t>
+  </si>
+  <si>
+    <t>275℃×9.5h</t>
+  </si>
+  <si>
+    <t>275℃×8h</t>
+  </si>
+  <si>
+    <t>400℃×24h+420℃×24h</t>
+  </si>
+  <si>
+    <t>422℃×2h</t>
+  </si>
+  <si>
+    <t>173℃×10h</t>
+  </si>
+  <si>
+    <t>450℃×24h+460℃×24h</t>
+  </si>
+  <si>
+    <t>465℃×2h</t>
+  </si>
+  <si>
+    <t>120℃×9h</t>
+  </si>
+  <si>
+    <t>120℃×24h</t>
+  </si>
+  <si>
+    <t>均匀化退火</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>固溶</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>时效</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>固溶温度</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>520</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="1"/>
+      </rPr>
+      <t>℃</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>465</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="1"/>
+      </rPr>
+      <t>℃</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>422</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="1"/>
+      </rPr>
+      <t>℃</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UTS</t>
+  </si>
+  <si>
+    <t>EL</t>
+  </si>
 </sst>
 </file>
 
@@ -299,7 +402,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0.0"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -334,6 +437,27 @@
       <family val="3"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="18"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="1"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <color theme="1"/>
+      <name val="Segoe UI Symbol"/>
+      <family val="1"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -358,10 +482,13 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -401,15 +528,6 @@
     <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -422,9 +540,22 @@
     <xf numFmtId="176" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="常规 2" xfId="1" xr:uid="{A0BE45A0-88DD-4714-BB86-0A2476432151}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1314,13 +1445,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C107522-3658-4374-ADB5-6BA5ABF96BD6}">
-  <dimension ref="A1:V27"/>
+  <dimension ref="A1:V44"/>
   <sheetFormatPr defaultRowHeight="22.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.77734375" style="10" bestFit="1" customWidth="1"/>
     <col min="2" max="7" width="8" style="10" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="9.88671875" style="10" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5546875" style="10" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="35.44140625" style="10" customWidth="1"/>
     <col min="10" max="10" width="20.6640625" style="10" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="19.88671875" style="10" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="16.33203125" style="10" bestFit="1" customWidth="1"/>
@@ -1408,15 +1539,15 @@
       <c r="L2" s="7">
         <v>705.07252900000003</v>
       </c>
-      <c r="M2" s="17" t="s">
+      <c r="M2" s="22" t="s">
         <v>23</v>
       </c>
-      <c r="N2" s="17"/>
-      <c r="O2" s="17"/>
-      <c r="P2" s="17"/>
-      <c r="Q2" s="17"/>
-      <c r="R2" s="17"/>
-      <c r="S2" s="17"/>
+      <c r="N2" s="22"/>
+      <c r="O2" s="22"/>
+      <c r="P2" s="22"/>
+      <c r="Q2" s="22"/>
+      <c r="R2" s="22"/>
+      <c r="S2" s="22"/>
       <c r="T2" s="12"/>
       <c r="U2" s="12"/>
       <c r="V2" s="12"/>
@@ -1458,13 +1589,13 @@
       <c r="L3" s="7">
         <v>699.91853700000001</v>
       </c>
-      <c r="M3" s="17"/>
-      <c r="N3" s="17"/>
-      <c r="O3" s="17"/>
-      <c r="P3" s="17"/>
-      <c r="Q3" s="17"/>
-      <c r="R3" s="17"/>
-      <c r="S3" s="17"/>
+      <c r="M3" s="22"/>
+      <c r="N3" s="22"/>
+      <c r="O3" s="22"/>
+      <c r="P3" s="22"/>
+      <c r="Q3" s="22"/>
+      <c r="R3" s="22"/>
+      <c r="S3" s="22"/>
       <c r="T3" s="12"/>
       <c r="U3" s="12"/>
       <c r="V3" s="12"/>
@@ -1506,13 +1637,13 @@
       <c r="L4" s="7">
         <v>693.71326299999998</v>
       </c>
-      <c r="M4" s="17"/>
-      <c r="N4" s="17"/>
-      <c r="O4" s="17"/>
-      <c r="P4" s="17"/>
-      <c r="Q4" s="17"/>
-      <c r="R4" s="17"/>
-      <c r="S4" s="17"/>
+      <c r="M4" s="22"/>
+      <c r="N4" s="22"/>
+      <c r="O4" s="22"/>
+      <c r="P4" s="22"/>
+      <c r="Q4" s="22"/>
+      <c r="R4" s="22"/>
+      <c r="S4" s="22"/>
       <c r="T4" s="12"/>
       <c r="U4" s="12"/>
       <c r="V4" s="12"/>
@@ -1554,13 +1685,13 @@
       <c r="L5" s="7">
         <v>687.800251</v>
       </c>
-      <c r="M5" s="17"/>
-      <c r="N5" s="17"/>
-      <c r="O5" s="17"/>
-      <c r="P5" s="17"/>
-      <c r="Q5" s="17"/>
-      <c r="R5" s="17"/>
-      <c r="S5" s="17"/>
+      <c r="M5" s="22"/>
+      <c r="N5" s="22"/>
+      <c r="O5" s="22"/>
+      <c r="P5" s="22"/>
+      <c r="Q5" s="22"/>
+      <c r="R5" s="22"/>
+      <c r="S5" s="22"/>
       <c r="T5" s="12"/>
       <c r="U5" s="12"/>
       <c r="V5" s="12"/>
@@ -1602,13 +1733,13 @@
       <c r="L6" s="7">
         <v>680.894678</v>
       </c>
-      <c r="M6" s="17"/>
-      <c r="N6" s="17"/>
-      <c r="O6" s="17"/>
-      <c r="P6" s="17"/>
-      <c r="Q6" s="17"/>
-      <c r="R6" s="17"/>
-      <c r="S6" s="17"/>
+      <c r="M6" s="22"/>
+      <c r="N6" s="22"/>
+      <c r="O6" s="22"/>
+      <c r="P6" s="22"/>
+      <c r="Q6" s="22"/>
+      <c r="R6" s="22"/>
+      <c r="S6" s="22"/>
       <c r="T6" s="12"/>
       <c r="U6" s="12"/>
       <c r="V6" s="12"/>
@@ -1673,15 +1804,15 @@
       <c r="L8" s="7">
         <v>693.71326299999998</v>
       </c>
-      <c r="M8" s="16" t="s">
+      <c r="M8" s="21" t="s">
         <v>24</v>
       </c>
-      <c r="N8" s="16"/>
-      <c r="O8" s="16"/>
-      <c r="P8" s="16"/>
-      <c r="Q8" s="16"/>
-      <c r="R8" s="16"/>
-      <c r="S8" s="16"/>
+      <c r="N8" s="21"/>
+      <c r="O8" s="21"/>
+      <c r="P8" s="21"/>
+      <c r="Q8" s="21"/>
+      <c r="R8" s="21"/>
+      <c r="S8" s="21"/>
       <c r="T8" s="14"/>
       <c r="U8" s="14"/>
       <c r="V8" s="14"/>
@@ -1723,13 +1854,13 @@
       <c r="L9" s="7">
         <v>693.71326299999998</v>
       </c>
-      <c r="M9" s="16"/>
-      <c r="N9" s="16"/>
-      <c r="O9" s="16"/>
-      <c r="P9" s="16"/>
-      <c r="Q9" s="16"/>
-      <c r="R9" s="16"/>
-      <c r="S9" s="16"/>
+      <c r="M9" s="21"/>
+      <c r="N9" s="21"/>
+      <c r="O9" s="21"/>
+      <c r="P9" s="21"/>
+      <c r="Q9" s="21"/>
+      <c r="R9" s="21"/>
+      <c r="S9" s="21"/>
       <c r="T9" s="14"/>
       <c r="U9" s="14"/>
       <c r="V9" s="14"/>
@@ -1794,15 +1925,15 @@
       <c r="L11" s="7">
         <v>655.86</v>
       </c>
-      <c r="M11" s="17" t="s">
+      <c r="M11" s="22" t="s">
         <v>25</v>
       </c>
-      <c r="N11" s="17"/>
-      <c r="O11" s="17"/>
-      <c r="P11" s="17"/>
-      <c r="Q11" s="17"/>
-      <c r="R11" s="17"/>
-      <c r="S11" s="17"/>
+      <c r="N11" s="22"/>
+      <c r="O11" s="22"/>
+      <c r="P11" s="22"/>
+      <c r="Q11" s="22"/>
+      <c r="R11" s="22"/>
+      <c r="S11" s="22"/>
       <c r="T11" s="13"/>
       <c r="U11" s="13"/>
       <c r="V11" s="13"/>
@@ -1844,13 +1975,13 @@
       <c r="L12" s="7">
         <v>650.63</v>
       </c>
-      <c r="M12" s="17"/>
-      <c r="N12" s="17"/>
-      <c r="O12" s="17"/>
-      <c r="P12" s="17"/>
-      <c r="Q12" s="17"/>
-      <c r="R12" s="17"/>
-      <c r="S12" s="17"/>
+      <c r="M12" s="22"/>
+      <c r="N12" s="22"/>
+      <c r="O12" s="22"/>
+      <c r="P12" s="22"/>
+      <c r="Q12" s="22"/>
+      <c r="R12" s="22"/>
+      <c r="S12" s="22"/>
       <c r="T12" s="13"/>
       <c r="U12" s="13"/>
       <c r="V12" s="13"/>
@@ -1892,13 +2023,13 @@
       <c r="L13" s="7">
         <v>654.62</v>
       </c>
-      <c r="M13" s="17"/>
-      <c r="N13" s="17"/>
-      <c r="O13" s="17"/>
-      <c r="P13" s="17"/>
-      <c r="Q13" s="17"/>
-      <c r="R13" s="17"/>
-      <c r="S13" s="17"/>
+      <c r="M13" s="22"/>
+      <c r="N13" s="22"/>
+      <c r="O13" s="22"/>
+      <c r="P13" s="22"/>
+      <c r="Q13" s="22"/>
+      <c r="R13" s="22"/>
+      <c r="S13" s="22"/>
       <c r="T13" s="13"/>
       <c r="U13" s="13"/>
       <c r="V13" s="13"/>
@@ -1975,231 +2106,231 @@
       <c r="V15" s="7"/>
     </row>
     <row r="16" spans="1:22" ht="22.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="18">
+      <c r="A16" s="15">
         <v>1</v>
       </c>
-      <c r="B16" s="19">
-        <v>0</v>
-      </c>
-      <c r="C16" s="19">
+      <c r="B16" s="16">
+        <v>0</v>
+      </c>
+      <c r="C16" s="16">
         <v>0.117345</v>
       </c>
-      <c r="D16" s="19">
+      <c r="D16" s="16">
         <v>7.0828069999999999</v>
       </c>
-      <c r="E16" s="19">
+      <c r="E16" s="16">
         <v>0.13770299999999999</v>
       </c>
-      <c r="F16" s="19">
+      <c r="F16" s="16">
         <v>5.0457000000000002E-2</v>
       </c>
-      <c r="G16" s="19">
-        <v>0</v>
-      </c>
-      <c r="H16" s="19">
+      <c r="G16" s="16">
+        <v>0</v>
+      </c>
+      <c r="H16" s="16">
         <v>92.611688000000001</v>
       </c>
-      <c r="I16" s="20">
+      <c r="I16" s="17">
         <v>523.49421099999995</v>
       </c>
-      <c r="J16" s="20">
+      <c r="J16" s="17">
         <v>306.16425299999997</v>
       </c>
-      <c r="K16" s="21">
+      <c r="K16" s="18">
         <v>5.0267999999999997</v>
       </c>
-      <c r="L16" s="19">
+      <c r="L16" s="16">
         <v>198.88639800000001</v>
       </c>
-      <c r="M16" s="16" t="s">
+      <c r="M16" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="N16" s="17"/>
-      <c r="O16" s="17"/>
-      <c r="P16" s="17"/>
-      <c r="Q16" s="17"/>
-      <c r="R16" s="17"/>
-      <c r="S16" s="17"/>
+      <c r="N16" s="22"/>
+      <c r="O16" s="22"/>
+      <c r="P16" s="22"/>
+      <c r="Q16" s="22"/>
+      <c r="R16" s="22"/>
+      <c r="S16" s="22"/>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A17" s="18">
+      <c r="A17" s="15">
         <v>2</v>
       </c>
-      <c r="B17" s="19">
+      <c r="B17" s="16">
         <v>2.7545459999999999</v>
       </c>
-      <c r="C17" s="19">
+      <c r="C17" s="16">
         <v>0.869448</v>
       </c>
-      <c r="D17" s="19">
+      <c r="D17" s="16">
         <v>6.7877109999999998</v>
       </c>
-      <c r="E17" s="19">
+      <c r="E17" s="16">
         <v>6.5535999999999997E-2</v>
       </c>
-      <c r="F17" s="19">
+      <c r="F17" s="16">
         <v>4.3603999999999997E-2</v>
       </c>
-      <c r="G17" s="19">
+      <c r="G17" s="16">
         <v>9.3499999999999996E-4</v>
       </c>
-      <c r="H17" s="19">
+      <c r="H17" s="16">
         <v>89.478219999999993</v>
       </c>
-      <c r="I17" s="20">
+      <c r="I17" s="17">
         <v>520.40509699999996</v>
       </c>
-      <c r="J17" s="20">
+      <c r="J17" s="17">
         <v>275.48826500000001</v>
       </c>
-      <c r="K17" s="21">
+      <c r="K17" s="18">
         <v>9.3545940000000005</v>
       </c>
-      <c r="L17" s="19">
+      <c r="L17" s="16">
         <v>299.90802000000002</v>
       </c>
-      <c r="M17" s="17"/>
-      <c r="N17" s="17"/>
-      <c r="O17" s="17"/>
-      <c r="P17" s="17"/>
-      <c r="Q17" s="17"/>
-      <c r="R17" s="17"/>
-      <c r="S17" s="17"/>
+      <c r="M17" s="22"/>
+      <c r="N17" s="22"/>
+      <c r="O17" s="22"/>
+      <c r="P17" s="22"/>
+      <c r="Q17" s="22"/>
+      <c r="R17" s="22"/>
+      <c r="S17" s="22"/>
     </row>
     <row r="18" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A18" s="18">
+      <c r="A18" s="15">
         <v>3</v>
       </c>
-      <c r="B18" s="19">
+      <c r="B18" s="16">
         <v>2.202499</v>
       </c>
-      <c r="C18" s="19">
+      <c r="C18" s="16">
         <v>1.3599399999999999</v>
       </c>
-      <c r="D18" s="19">
+      <c r="D18" s="16">
         <v>7.0022760000000002</v>
       </c>
-      <c r="E18" s="19">
-        <v>0</v>
-      </c>
-      <c r="F18" s="19">
+      <c r="E18" s="16">
+        <v>0</v>
+      </c>
+      <c r="F18" s="16">
         <v>5.3226999999999997E-2</v>
       </c>
-      <c r="G18" s="19">
+      <c r="G18" s="16">
         <v>0.13575000000000001</v>
       </c>
-      <c r="H18" s="19">
+      <c r="H18" s="16">
         <v>89.246307999999999</v>
       </c>
-      <c r="I18" s="20">
+      <c r="I18" s="17">
         <v>520.17504399999996</v>
       </c>
-      <c r="J18" s="20">
+      <c r="J18" s="17">
         <v>272.92353800000001</v>
       </c>
-      <c r="K18" s="21">
+      <c r="K18" s="18">
         <v>8.0743200000000002</v>
       </c>
-      <c r="L18" s="19">
+      <c r="L18" s="16">
         <v>400.101562</v>
       </c>
-      <c r="M18" s="17"/>
-      <c r="N18" s="17"/>
-      <c r="O18" s="17"/>
-      <c r="P18" s="17"/>
-      <c r="Q18" s="17"/>
-      <c r="R18" s="17"/>
-      <c r="S18" s="17"/>
+      <c r="M18" s="22"/>
+      <c r="N18" s="22"/>
+      <c r="O18" s="22"/>
+      <c r="P18" s="22"/>
+      <c r="Q18" s="22"/>
+      <c r="R18" s="22"/>
+      <c r="S18" s="22"/>
     </row>
     <row r="19" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A19" s="18">
+      <c r="A19" s="15">
         <v>4</v>
       </c>
-      <c r="B19" s="19">
+      <c r="B19" s="16">
         <v>4.3163929999999997</v>
       </c>
-      <c r="C19" s="19">
+      <c r="C19" s="16">
         <v>2.0737839999999998</v>
       </c>
-      <c r="D19" s="19">
+      <c r="D19" s="16">
         <v>6.4016719999999996</v>
       </c>
-      <c r="E19" s="19">
+      <c r="E19" s="16">
         <v>3.1909999999999998E-3</v>
       </c>
-      <c r="F19" s="19">
+      <c r="F19" s="16">
         <v>3.4314999999999998E-2</v>
       </c>
-      <c r="G19" s="19">
+      <c r="G19" s="16">
         <v>9.8548999999999998E-2</v>
       </c>
-      <c r="H19" s="19">
+      <c r="H19" s="16">
         <v>87.072096000000002</v>
       </c>
-      <c r="I19" s="20">
+      <c r="I19" s="17">
         <v>421.56461400000001</v>
       </c>
-      <c r="J19" s="20">
+      <c r="J19" s="17">
         <v>172.80068900000001</v>
       </c>
-      <c r="K19" s="21">
+      <c r="K19" s="18">
         <v>10.037141999999999</v>
       </c>
-      <c r="L19" s="19">
+      <c r="L19" s="16">
         <v>500.01162699999998</v>
       </c>
-      <c r="M19" s="17"/>
-      <c r="N19" s="17"/>
-      <c r="O19" s="17"/>
-      <c r="P19" s="17"/>
-      <c r="Q19" s="17"/>
-      <c r="R19" s="17"/>
-      <c r="S19" s="17"/>
+      <c r="M19" s="22"/>
+      <c r="N19" s="22"/>
+      <c r="O19" s="22"/>
+      <c r="P19" s="22"/>
+      <c r="Q19" s="22"/>
+      <c r="R19" s="22"/>
+      <c r="S19" s="22"/>
     </row>
     <row r="20" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A20" s="18">
+      <c r="A20" s="15">
         <v>5</v>
       </c>
-      <c r="B20" s="19">
+      <c r="B20" s="16">
         <v>5.5428069999999998</v>
       </c>
-      <c r="C20" s="19">
+      <c r="C20" s="16">
         <v>2.5891519999999999</v>
       </c>
-      <c r="D20" s="19">
+      <c r="D20" s="16">
         <v>6.5263540000000004</v>
       </c>
-      <c r="E20" s="19">
+      <c r="E20" s="16">
         <v>0.17667099999999999</v>
       </c>
-      <c r="F20" s="19">
+      <c r="F20" s="16">
         <v>4.8640999999999997E-2</v>
       </c>
-      <c r="G20" s="19">
+      <c r="G20" s="16">
         <v>0.115828</v>
       </c>
-      <c r="H20" s="19">
+      <c r="H20" s="16">
         <v>85.000546999999997</v>
       </c>
-      <c r="I20" s="20">
+      <c r="I20" s="17">
         <v>469.28150699999998</v>
       </c>
-      <c r="J20" s="20">
+      <c r="J20" s="17">
         <v>117.077184</v>
       </c>
-      <c r="K20" s="21">
+      <c r="K20" s="18">
         <v>9.0460560000000001</v>
       </c>
-      <c r="L20" s="19">
+      <c r="L20" s="16">
         <v>600.35815400000001</v>
       </c>
-      <c r="M20" s="17"/>
-      <c r="N20" s="17"/>
-      <c r="O20" s="17"/>
-      <c r="P20" s="17"/>
-      <c r="Q20" s="17"/>
-      <c r="R20" s="17"/>
-      <c r="S20" s="17"/>
+      <c r="M20" s="22"/>
+      <c r="N20" s="22"/>
+      <c r="O20" s="22"/>
+      <c r="P20" s="22"/>
+      <c r="Q20" s="22"/>
+      <c r="R20" s="22"/>
+      <c r="S20" s="22"/>
     </row>
     <row r="21" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A21" s="10">
@@ -2238,13 +2369,13 @@
       <c r="L21" s="7">
         <v>596.45180100000005</v>
       </c>
-      <c r="M21" s="17"/>
-      <c r="N21" s="17"/>
-      <c r="O21" s="17"/>
-      <c r="P21" s="17"/>
-      <c r="Q21" s="17"/>
-      <c r="R21" s="17"/>
-      <c r="S21" s="17"/>
+      <c r="M21" s="22"/>
+      <c r="N21" s="22"/>
+      <c r="O21" s="22"/>
+      <c r="P21" s="22"/>
+      <c r="Q21" s="22"/>
+      <c r="R21" s="22"/>
+      <c r="S21" s="22"/>
     </row>
     <row r="23" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A23" s="10">
@@ -2283,60 +2414,60 @@
       <c r="L23" s="7">
         <v>680.894678</v>
       </c>
-      <c r="M23" s="15" t="s">
+      <c r="M23" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="N23" s="16"/>
-      <c r="O23" s="16"/>
-      <c r="P23" s="16"/>
-      <c r="Q23" s="16"/>
-      <c r="R23" s="16"/>
-      <c r="S23" s="16"/>
+      <c r="N23" s="21"/>
+      <c r="O23" s="21"/>
+      <c r="P23" s="21"/>
+      <c r="Q23" s="21"/>
+      <c r="R23" s="21"/>
+      <c r="S23" s="21"/>
     </row>
     <row r="24" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A24" s="18">
+      <c r="A24" s="15">
         <v>8</v>
       </c>
-      <c r="B24" s="19">
+      <c r="B24" s="16">
         <v>7.3892499999999997</v>
       </c>
-      <c r="C24" s="19">
+      <c r="C24" s="16">
         <v>2.5963820000000002</v>
       </c>
-      <c r="D24" s="19">
+      <c r="D24" s="16">
         <v>2.497541</v>
       </c>
-      <c r="E24" s="19">
+      <c r="E24" s="16">
         <v>0.237843</v>
       </c>
-      <c r="F24" s="19">
+      <c r="F24" s="16">
         <v>5.6372999999999999E-2</v>
       </c>
-      <c r="G24" s="19">
+      <c r="G24" s="16">
         <v>0.16356000000000001</v>
       </c>
-      <c r="H24" s="19">
+      <c r="H24" s="16">
         <v>87.054609999999997</v>
       </c>
-      <c r="I24" s="20">
+      <c r="I24" s="17">
         <v>461.61370699999998</v>
       </c>
-      <c r="J24" s="20">
+      <c r="J24" s="17">
         <v>122.741788</v>
       </c>
-      <c r="K24" s="21">
+      <c r="K24" s="18">
         <v>24.003623000000001</v>
       </c>
-      <c r="L24" s="19">
+      <c r="L24" s="16">
         <v>705.07252900000003</v>
       </c>
-      <c r="M24" s="16"/>
-      <c r="N24" s="16"/>
-      <c r="O24" s="16"/>
-      <c r="P24" s="16"/>
-      <c r="Q24" s="16"/>
-      <c r="R24" s="16"/>
-      <c r="S24" s="16"/>
+      <c r="M24" s="21"/>
+      <c r="N24" s="21"/>
+      <c r="O24" s="21"/>
+      <c r="P24" s="21"/>
+      <c r="Q24" s="21"/>
+      <c r="R24" s="21"/>
+      <c r="S24" s="21"/>
     </row>
     <row r="25" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B25" s="7"/>
@@ -2388,15 +2519,15 @@
       <c r="L26" s="7">
         <v>705.07252900000003</v>
       </c>
-      <c r="M26" s="15" t="s">
+      <c r="M26" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="N26" s="16"/>
-      <c r="O26" s="16"/>
-      <c r="P26" s="16"/>
-      <c r="Q26" s="16"/>
-      <c r="R26" s="16"/>
-      <c r="S26" s="16"/>
+      <c r="N26" s="21"/>
+      <c r="O26" s="21"/>
+      <c r="P26" s="21"/>
+      <c r="Q26" s="21"/>
+      <c r="R26" s="21"/>
+      <c r="S26" s="21"/>
     </row>
     <row r="27" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A27" s="10">
@@ -2435,13 +2566,524 @@
       <c r="L27" s="7">
         <v>705.07252900000003</v>
       </c>
-      <c r="M27" s="16"/>
-      <c r="N27" s="16"/>
-      <c r="O27" s="16"/>
-      <c r="P27" s="16"/>
-      <c r="Q27" s="16"/>
-      <c r="R27" s="16"/>
-      <c r="S27" s="16"/>
+      <c r="M27" s="21"/>
+      <c r="N27" s="21"/>
+      <c r="O27" s="21"/>
+      <c r="P27" s="21"/>
+      <c r="Q27" s="21"/>
+      <c r="R27" s="21"/>
+      <c r="S27" s="21"/>
+    </row>
+    <row r="30" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A30" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="B30" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C30" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="D30" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="E30" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F30" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="G30" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="H30" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="I30" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="J30" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="K30" s="19" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="31" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A31" s="10">
+        <v>1</v>
+      </c>
+      <c r="B31" s="7">
+        <v>0</v>
+      </c>
+      <c r="C31" s="7">
+        <v>0.117345</v>
+      </c>
+      <c r="D31" s="7">
+        <v>7.0828069999999999</v>
+      </c>
+      <c r="E31" s="7">
+        <v>0.13770299999999999</v>
+      </c>
+      <c r="F31" s="7">
+        <v>5.0457000000000002E-2</v>
+      </c>
+      <c r="G31" s="7">
+        <v>0</v>
+      </c>
+      <c r="H31" s="7">
+        <v>92.611688000000001</v>
+      </c>
+      <c r="I31" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="J31" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="K31" s="7" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="32" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A32" s="10">
+        <v>2</v>
+      </c>
+      <c r="B32" s="7">
+        <v>2.7545459999999999</v>
+      </c>
+      <c r="C32" s="7">
+        <v>0.869448</v>
+      </c>
+      <c r="D32" s="7">
+        <v>6.7877109999999998</v>
+      </c>
+      <c r="E32" s="7">
+        <v>6.5535999999999997E-2</v>
+      </c>
+      <c r="F32" s="7">
+        <v>4.3603999999999997E-2</v>
+      </c>
+      <c r="G32" s="7">
+        <v>9.3499999999999996E-4</v>
+      </c>
+      <c r="H32" s="7">
+        <v>89.478219999999993</v>
+      </c>
+      <c r="I32" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="J32" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="K32" s="7" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A33" s="10">
+        <v>3</v>
+      </c>
+      <c r="B33" s="7">
+        <v>2.202499</v>
+      </c>
+      <c r="C33" s="7">
+        <v>1.3599399999999999</v>
+      </c>
+      <c r="D33" s="7">
+        <v>7.0022760000000002</v>
+      </c>
+      <c r="E33" s="7">
+        <v>0</v>
+      </c>
+      <c r="F33" s="7">
+        <v>5.3226999999999997E-2</v>
+      </c>
+      <c r="G33" s="7">
+        <v>0.13575000000000001</v>
+      </c>
+      <c r="H33" s="7">
+        <v>89.246307999999999</v>
+      </c>
+      <c r="I33" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="J33" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="K33" s="7" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A34" s="10">
+        <v>4</v>
+      </c>
+      <c r="B34" s="7">
+        <v>4.3163929999999997</v>
+      </c>
+      <c r="C34" s="7">
+        <v>2.0737839999999998</v>
+      </c>
+      <c r="D34" s="7">
+        <v>6.4016719999999996</v>
+      </c>
+      <c r="E34" s="7">
+        <v>3.1909999999999998E-3</v>
+      </c>
+      <c r="F34" s="7">
+        <v>3.4314999999999998E-2</v>
+      </c>
+      <c r="G34" s="7">
+        <v>9.8548999999999998E-2</v>
+      </c>
+      <c r="H34" s="7">
+        <v>87.072096000000002</v>
+      </c>
+      <c r="I34" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="J34" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="K34" s="7" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A35" s="10">
+        <v>5</v>
+      </c>
+      <c r="B35" s="7">
+        <v>5.5428069999999998</v>
+      </c>
+      <c r="C35" s="7">
+        <v>2.5891519999999999</v>
+      </c>
+      <c r="D35" s="7">
+        <v>6.5263540000000004</v>
+      </c>
+      <c r="E35" s="7">
+        <v>0.17667099999999999</v>
+      </c>
+      <c r="F35" s="7">
+        <v>4.8640999999999997E-2</v>
+      </c>
+      <c r="G35" s="7">
+        <v>0.115828</v>
+      </c>
+      <c r="H35" s="7">
+        <v>85.000546999999997</v>
+      </c>
+      <c r="I35" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="J35" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="K35" s="7" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A36" s="10">
+        <v>6</v>
+      </c>
+      <c r="B36" s="7">
+        <v>7.3892499999999997</v>
+      </c>
+      <c r="C36" s="7">
+        <v>2.5963820000000002</v>
+      </c>
+      <c r="D36" s="7">
+        <v>2.497541</v>
+      </c>
+      <c r="E36" s="7">
+        <v>0.237843</v>
+      </c>
+      <c r="F36" s="7">
+        <v>5.6372999999999999E-2</v>
+      </c>
+      <c r="G36" s="7">
+        <v>0.16356000000000001</v>
+      </c>
+      <c r="H36" s="7">
+        <v>87.054609999999997</v>
+      </c>
+      <c r="I36" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="J36" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="K36" s="7" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A38" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="B38" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C38" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="D38" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="E38" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F38" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="G38" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="H38" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="I38" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="J38" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="K38" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="L38" s="10" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" ht="27" x14ac:dyDescent="0.25">
+      <c r="A39" s="10">
+        <v>1</v>
+      </c>
+      <c r="B39" s="7">
+        <v>0</v>
+      </c>
+      <c r="C39" s="7">
+        <v>0.117345</v>
+      </c>
+      <c r="D39" s="7">
+        <v>7.0828069999999999</v>
+      </c>
+      <c r="E39" s="7">
+        <v>0.13770299999999999</v>
+      </c>
+      <c r="F39" s="7">
+        <v>5.0457000000000002E-2</v>
+      </c>
+      <c r="G39" s="7">
+        <v>0</v>
+      </c>
+      <c r="H39" s="7">
+        <v>92.611688000000001</v>
+      </c>
+      <c r="I39" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="J39" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="K39" s="10">
+        <v>198.89</v>
+      </c>
+      <c r="L39" s="10">
+        <v>22.74</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" ht="27" x14ac:dyDescent="0.25">
+      <c r="A40" s="10">
+        <v>2</v>
+      </c>
+      <c r="B40" s="7">
+        <v>2.7545459999999999</v>
+      </c>
+      <c r="C40" s="7">
+        <v>0.869448</v>
+      </c>
+      <c r="D40" s="7">
+        <v>6.7877109999999998</v>
+      </c>
+      <c r="E40" s="7">
+        <v>6.5535999999999997E-2</v>
+      </c>
+      <c r="F40" s="7">
+        <v>4.3603999999999997E-2</v>
+      </c>
+      <c r="G40" s="7">
+        <v>9.3499999999999996E-4</v>
+      </c>
+      <c r="H40" s="7">
+        <v>89.478219999999993</v>
+      </c>
+      <c r="I40" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="J40" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="K40" s="10">
+        <v>299.91000000000003</v>
+      </c>
+      <c r="L40" s="10">
+        <v>23.85</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" ht="27" x14ac:dyDescent="0.25">
+      <c r="A41" s="10">
+        <v>3</v>
+      </c>
+      <c r="B41" s="7">
+        <v>2.202499</v>
+      </c>
+      <c r="C41" s="7">
+        <v>1.3599399999999999</v>
+      </c>
+      <c r="D41" s="7">
+        <v>7.0022760000000002</v>
+      </c>
+      <c r="E41" s="7">
+        <v>0</v>
+      </c>
+      <c r="F41" s="7">
+        <v>5.3226999999999997E-2</v>
+      </c>
+      <c r="G41" s="7">
+        <v>0.13575000000000001</v>
+      </c>
+      <c r="H41" s="7">
+        <v>89.246307999999999</v>
+      </c>
+      <c r="I41" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="J41" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="K41" s="10">
+        <v>306.47000000000003</v>
+      </c>
+      <c r="L41" s="10">
+        <v>23.2</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" ht="27" x14ac:dyDescent="0.25">
+      <c r="A42" s="10">
+        <v>4</v>
+      </c>
+      <c r="B42" s="7">
+        <v>4.3163929999999997</v>
+      </c>
+      <c r="C42" s="7">
+        <v>2.0737839999999998</v>
+      </c>
+      <c r="D42" s="7">
+        <v>6.4016719999999996</v>
+      </c>
+      <c r="E42" s="7">
+        <v>3.1909999999999998E-3</v>
+      </c>
+      <c r="F42" s="7">
+        <v>3.4314999999999998E-2</v>
+      </c>
+      <c r="G42" s="7">
+        <v>9.8548999999999998E-2</v>
+      </c>
+      <c r="H42" s="7">
+        <v>87.072096000000002</v>
+      </c>
+      <c r="I42" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="J42" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="K42" s="10">
+        <v>500.61</v>
+      </c>
+      <c r="L42" s="10">
+        <v>23.22</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" ht="27" x14ac:dyDescent="0.25">
+      <c r="A43" s="10">
+        <v>5</v>
+      </c>
+      <c r="B43" s="7">
+        <v>5.5428069999999998</v>
+      </c>
+      <c r="C43" s="7">
+        <v>2.5891519999999999</v>
+      </c>
+      <c r="D43" s="7">
+        <v>6.5263540000000004</v>
+      </c>
+      <c r="E43" s="7">
+        <v>0.17667099999999999</v>
+      </c>
+      <c r="F43" s="7">
+        <v>4.8640999999999997E-2</v>
+      </c>
+      <c r="G43" s="7">
+        <v>0.115828</v>
+      </c>
+      <c r="H43" s="7">
+        <v>85.000546999999997</v>
+      </c>
+      <c r="I43" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="J43" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="K43" s="10">
+        <v>596.78</v>
+      </c>
+      <c r="L43" s="10">
+        <v>23.22</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" ht="27" x14ac:dyDescent="0.25">
+      <c r="A44" s="10">
+        <v>6</v>
+      </c>
+      <c r="B44" s="7">
+        <v>7.3892499999999997</v>
+      </c>
+      <c r="C44" s="7">
+        <v>2.5963820000000002</v>
+      </c>
+      <c r="D44" s="7">
+        <v>2.497541</v>
+      </c>
+      <c r="E44" s="7">
+        <v>0.237843</v>
+      </c>
+      <c r="F44" s="7">
+        <v>5.6372999999999999E-2</v>
+      </c>
+      <c r="G44" s="7">
+        <v>0.16356000000000001</v>
+      </c>
+      <c r="H44" s="7">
+        <v>87.054609999999997</v>
+      </c>
+      <c r="I44" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="J44" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="K44" s="10">
+        <v>687.68</v>
+      </c>
+      <c r="L44" s="10">
+        <v>23.22</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="6">
